--- a/psychopy_exp_files/sequences/learning_block2_fixed-middle-10_09.xlsx
+++ b/psychopy_exp_files/sequences/learning_block2_fixed-middle-10_09.xlsx
@@ -574,12 +574,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_25.jpg</t>
+          <t>stimuli/dog/dog_40.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_08.jpg</t>
+          <t>stimuli/chair/chair_26.jpg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -594,17 +594,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -614,18 +614,18 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -638,10 +638,10 @@
         <v>12</v>
       </c>
       <c r="V2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -673,12 +673,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_26.jpg</t>
+          <t>stimuli/hammer/hammer_39.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_38.jpg</t>
+          <t>stimuli/phone/phone_27.jpg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -693,38 +693,38 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.31</v>
+        <v>0.25</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -737,10 +737,10 @@
         <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -772,12 +772,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/ball/ball_50.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_27.jpg</t>
+          <t>stimuli/bicycle/bicycle_08.jpg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,22 +792,22 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -816,14 +816,14 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.31</v>
+        <v>0.42</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -836,10 +836,10 @@
         <v>9</v>
       </c>
       <c r="V4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -871,12 +871,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_50.jpg</t>
+          <t>stimuli/jacket/jacket_15.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_26.jpg</t>
+          <t>stimuli/guitar/guitar_38.jpg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -891,38 +891,38 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.53</v>
+        <v>0.42</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S5" t="n">
@@ -935,10 +935,10 @@
         <v>5</v>
       </c>
       <c r="V5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="W5" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -970,12 +970,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_39.jpg</t>
+          <t>stimuli/hand/hand_24.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_38.jpg</t>
+          <t>stimuli/phone/phone_27.jpg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -990,22 +990,22 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1014,14 +1014,14 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -1034,10 +1034,10 @@
         <v>6</v>
       </c>
       <c r="V6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W6" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -1069,12 +1069,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/chair/chair_26.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_26.jpg</t>
+          <t>stimuli/lamp/lamp_35.jpg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1089,22 +1089,22 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1113,14 +1113,14 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0.8</v>
+        <v>0.64</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.64</v>
+        <v>0.4</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -1133,10 +1133,10 @@
         <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="W7" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -1168,12 +1168,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_26.jpg</t>
+          <t>stimuli/guitar/guitar_38.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/house/house_49.jpg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1188,12 +1188,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1212,10 +1212,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.4</v>
+        <v>0.58</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1232,10 +1232,10 @@
         <v>8</v>
       </c>
       <c r="V8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="W8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_35.jpg</t>
+          <t>stimuli/fish/fish_26.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/dog/dog_40.jpg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1287,12 +1287,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1331,10 +1331,10 @@
         <v>10</v>
       </c>
       <c r="V9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="W9" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -1366,12 +1366,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_38.jpg</t>
+          <t>stimuli/house/house_49.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_15.jpg</t>
+          <t>stimuli/flower/flower_25.jpg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1386,38 +1386,38 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.47</v>
+        <v>0.27</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S10" t="n">
@@ -1430,10 +1430,10 @@
         <v>7</v>
       </c>
       <c r="V10" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="W10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -1465,14 +1465,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>stimuli/lamp/lamp_35.jpg</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_15.jpg</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_50.jpg</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>hammer</t>
@@ -1485,14 +1485,14 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>left</t>
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="P11" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="Q11" t="n">
         <v>0.53</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.27</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -1529,10 +1529,10 @@
         <v>4</v>
       </c>
       <c r="V11" t="n">
+        <v>14</v>
+      </c>
+      <c r="W11" t="n">
         <v>3</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/fish/fish_26.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0.53</v>
+        <v>0.67</v>
       </c>
       <c r="Q12" t="n">
         <v>0.2</v>
@@ -1628,7 +1628,7 @@
         <v>2</v>
       </c>
       <c r="V12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="W12" t="n">
         <v>10</v>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/flower/flower_25.jpg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1688,17 +1688,17 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1710,11 +1710,11 @@
         <v>0.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S13" t="n">
@@ -1730,7 +1730,7 @@
         <v>14</v>
       </c>
       <c r="W13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_39.jpg</t>
+          <t>stimuli/dog/dog_40.jpg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1787,17 +1787,17 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1809,11 +1809,11 @@
         <v>0.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.27</v>
+        <v>0.6</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S14" t="n">
@@ -1829,7 +1829,7 @@
         <v>12</v>
       </c>
       <c r="W14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_05.jpg</t>
+          <t>stimuli/dog/dog_31.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1891,28 +1891,28 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="Q15" t="n">
         <v>0.31</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S15" t="n">
@@ -1925,7 +1925,7 @@
         <v>14</v>
       </c>
       <c r="V15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W15" t="n">
         <v>4</v>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1990,28 +1990,28 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0.47</v>
+        <v>0.75</v>
       </c>
       <c r="Q16" t="n">
         <v>0.25</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S16" t="n">
@@ -2024,7 +2024,7 @@
         <v>5</v>
       </c>
       <c r="V16" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="W16" t="n">
         <v>16</v>
@@ -2059,12 +2059,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/bread/bread_22.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_17.jpg</t>
+          <t>stimuli/key/key_13.jpg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2079,38 +2079,38 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.2</v>
+        <v>0.36</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S17" t="n">
@@ -2123,10 +2123,10 @@
         <v>10</v>
       </c>
       <c r="V17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -2158,12 +2158,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/ball/ball_14.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>stimuli/key/key_13.jpg</t>
+          <t>stimuli/hand/hand_28.jpg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2178,12 +2178,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2193,19 +2193,19 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.58</v>
+        <v>0.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.42</v>
+        <v>0.53</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -2222,10 +2222,10 @@
         <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="W18" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S19" t="n">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_33.jpg</t>
+          <t>stimuli/pencil/pencil_21.jpg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2381,33 +2381,33 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P20" t="n">
         <v>0.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S20" t="n">
@@ -2423,7 +2423,7 @@
         <v>7</v>
       </c>
       <c r="W20" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_01.jpg</t>
+          <t>stimuli/house/house_23.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_21.jpg</t>
+          <t>stimuli/chair/chair_33.jpg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2475,22 +2475,22 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2499,14 +2499,14 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.53</v>
+        <v>0.64</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S21" t="n">
@@ -2519,10 +2519,10 @@
         <v>7</v>
       </c>
       <c r="V21" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W21" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -2554,12 +2554,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_17.jpg</t>
+          <t>stimuli/lamp/lamp_03.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_11.jpg</t>
+          <t>stimuli/ball/ball_14.jpg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2574,22 +2574,22 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2598,14 +2598,14 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S22" t="n">
@@ -2618,10 +2618,10 @@
         <v>6</v>
       </c>
       <c r="V22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -2653,12 +2653,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_28.jpg</t>
+          <t>stimuli/jacket/jacket_05.jpg</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_21.jpg</t>
+          <t>stimuli/bread/bread_22.jpg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2673,17 +2673,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2693,18 +2693,18 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.64</v>
+        <v>0.2</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S23" t="n">
@@ -2717,10 +2717,10 @@
         <v>9</v>
       </c>
       <c r="V23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W23" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/jacket/jacket_05.jpg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2777,33 +2777,33 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P24" t="n">
         <v>0.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.27</v>
+        <v>0.47</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S24" t="n">
@@ -2819,7 +2819,7 @@
         <v>14</v>
       </c>
       <c r="W24" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_31.jpg</t>
+          <t>stimuli/guitar/guitar_17.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/flower/flower_01.jpg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2871,17 +2871,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2891,18 +2891,18 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S25" t="n">
@@ -2915,10 +2915,10 @@
         <v>4</v>
       </c>
       <c r="V25" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="W25" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_05.jpg</t>
+          <t>stimuli/dog/dog_31.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2980,28 +2980,28 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="Q26" t="n">
         <v>0.33</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S26" t="n">
@@ -3014,7 +3014,7 @@
         <v>15</v>
       </c>
       <c r="V26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W26" t="n">
         <v>7</v>
@@ -3049,12 +3049,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_03.jpg</t>
+          <t>stimuli/hammer/hammer_50.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/guitar/guitar_17.jpg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3069,17 +3069,17 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3089,18 +3089,18 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.47</v>
+        <v>0.26</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S27" t="n">
@@ -3113,10 +3113,10 @@
         <v>16</v>
       </c>
       <c r="V27" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="W27" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_25.jpg</t>
+          <t>stimuli/hand/hand_24.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_38.jpg</t>
+          <t>stimuli/bicycle/bicycle_08.jpg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3168,38 +3168,38 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0.64</v>
+        <v>0.53</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S28" t="n">
@@ -3212,10 +3212,10 @@
         <v>12</v>
       </c>
       <c r="V28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W28" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_15.jpg</t>
+          <t>stimuli/hammer/hammer_39.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_27.jpg</t>
+          <t>stimuli/guitar/guitar_38.jpg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3267,38 +3267,38 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S29" t="n">
@@ -3311,10 +3311,10 @@
         <v>3</v>
       </c>
       <c r="V29" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W29" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30">
@@ -3346,12 +3346,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_25.jpg</t>
+          <t>stimuli/bicycle/bicycle_08.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_26.jpg</t>
+          <t>stimuli/phone/phone_27.jpg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3366,38 +3366,38 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0.75</v>
+        <v>0.42</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.47</v>
+        <v>0.31</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S30" t="n">
@@ -3410,10 +3410,10 @@
         <v>9</v>
       </c>
       <c r="V30" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="W30" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/flower/flower_25.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3489,14 +3489,14 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="Q31" t="n">
         <v>0.27</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S31" t="n">
@@ -3509,7 +3509,7 @@
         <v>5</v>
       </c>
       <c r="V31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W31" t="n">
         <v>14</v>
@@ -3544,12 +3544,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_39.jpg</t>
+          <t>stimuli/jacket/jacket_15.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_27.jpg</t>
+          <t>stimuli/guitar/guitar_38.jpg</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3579,19 +3579,19 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
@@ -3608,10 +3608,10 @@
         <v>6</v>
       </c>
       <c r="V32" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W32" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_35.jpg</t>
+          <t>stimuli/hand/hand_24.jpg</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_15.jpg</t>
+          <t>stimuli/chair/chair_26.jpg</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3678,19 +3678,19 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.27</v>
+        <v>0.64</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
@@ -3707,10 +3707,10 @@
         <v>1</v>
       </c>
       <c r="V33" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="W33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_39.jpg</t>
+          <t>stimuli/fish/fish_26.jpg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_08.jpg</t>
+          <t>stimuli/house/house_49.jpg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3786,10 +3786,10 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.64</v>
+        <v>0.27</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
@@ -3806,10 +3806,10 @@
         <v>8</v>
       </c>
       <c r="V34" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="W34" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_08.jpg</t>
+          <t>stimuli/phone/phone_27.jpg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/dog/dog_40.jpg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3861,22 +3861,22 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3885,14 +3885,14 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S35" t="n">
@@ -3905,10 +3905,10 @@
         <v>10</v>
       </c>
       <c r="V35" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="W35" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_35.jpg</t>
+          <t>stimuli/house/house_49.jpg</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3970,28 +3970,28 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="Q36" t="n">
         <v>0.2</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S36" t="n">
@@ -4004,7 +4004,7 @@
         <v>7</v>
       </c>
       <c r="V36" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="W36" t="n">
         <v>1</v>
@@ -4039,12 +4039,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_26.jpg</t>
+          <t>stimuli/bread/bread_15.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/flower/flower_25.jpg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4059,22 +4059,22 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -4083,14 +4083,14 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0.6</v>
+        <v>0.53</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S37" t="n">
@@ -4103,10 +4103,10 @@
         <v>4</v>
       </c>
       <c r="V37" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="W37" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/house/house_49.jpg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4163,33 +4163,33 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P38" t="n">
         <v>0.73</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S38" t="n">
@@ -4205,7 +4205,7 @@
         <v>14</v>
       </c>
       <c r="W38" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_15.jpg</t>
+          <t>stimuli/fish/fish_26.jpg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4267,28 +4267,28 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="Q39" t="n">
         <v>0.33</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S39" t="n">
@@ -4301,7 +4301,7 @@
         <v>13</v>
       </c>
       <c r="V39" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="W39" t="n">
         <v>8</v>
@@ -4336,12 +4336,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_50.jpg</t>
+          <t>stimuli/bread/bread_15.jpg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_35.jpg</t>
+          <t>stimuli/dog/dog_40.jpg</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4356,38 +4356,38 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0.47</v>
+        <v>0.73</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.26</v>
+        <v>0.6</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S40" t="n">
@@ -4400,10 +4400,10 @@
         <v>17</v>
       </c>
       <c r="V40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W40" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>stimuli/key/key_13.jpg</t>
+          <t>stimuli/pencil/pencil_21.jpg</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4455,22 +4455,22 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -4479,14 +4479,14 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0.42</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S41" t="n">
@@ -4499,10 +4499,10 @@
         <v>14</v>
       </c>
       <c r="V41" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="W41" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42">
@@ -4534,14 +4534,14 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_50.jpg</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_33.jpg</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>stimuli/pencil/pencil_21.jpg</t>
-        </is>
-      </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>lamp</t>
@@ -4554,14 +4554,14 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
           <t>chair</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>pencil</t>
-        </is>
-      </c>
       <c r="M42" t="inlineStr">
         <is>
           <t>left</t>
@@ -4569,19 +4569,19 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P42" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="Q42" t="n">
         <v>0.36</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0.25</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
@@ -4598,10 +4598,10 @@
         <v>5</v>
       </c>
       <c r="V42" t="n">
+        <v>7</v>
+      </c>
+      <c r="W42" t="n">
         <v>4</v>
-      </c>
-      <c r="W42" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="43">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_01.jpg</t>
+          <t>stimuli/ball/ball_14.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_28.jpg</t>
+          <t>stimuli/key/key_13.jpg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4653,38 +4653,38 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0.58</v>
+        <v>0.75</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.47</v>
+        <v>0.36</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S43" t="n">
@@ -4697,10 +4697,10 @@
         <v>10</v>
       </c>
       <c r="V43" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W43" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/bread/bread_22.jpg</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_33.jpg</t>
+          <t>stimuli/hand/hand_28.jpg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4752,38 +4752,38 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S44" t="n">
@@ -4796,10 +4796,10 @@
         <v>2</v>
       </c>
       <c r="V44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W44" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_50.jpg</t>
+          <t>stimuli/flower/flower_01.jpg</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4861,28 +4861,28 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q45" t="n">
         <v>0.42</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S45" t="n">
@@ -4895,7 +4895,7 @@
         <v>1</v>
       </c>
       <c r="V45" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W45" t="n">
         <v>16</v>
@@ -4930,12 +4930,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_28.jpg</t>
+          <t>stimuli/hammer/hammer_50.jpg</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_03.jpg</t>
+          <t>stimuli/house/house_23.jpg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4950,38 +4950,38 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.33</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S46" t="n">
@@ -4994,10 +4994,10 @@
         <v>3</v>
       </c>
       <c r="V46" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W46" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>stimuli/key/key_13.jpg</t>
+          <t>stimuli/dog/dog_31.jpg</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5049,7 +5049,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -5059,12 +5059,12 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -5073,14 +5073,14 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0.58</v>
+        <v>0.33</v>
       </c>
       <c r="Q47" t="n">
         <v>0.2</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S47" t="n">
@@ -5093,7 +5093,7 @@
         <v>7</v>
       </c>
       <c r="V47" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="W47" t="n">
         <v>2</v>
@@ -5128,12 +5128,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_17.jpg</t>
+          <t>stimuli/pencil/pencil_21.jpg</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/lamp/lamp_03.jpg</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5148,38 +5148,38 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.2</v>
+        <v>0.47</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S48" t="n">
@@ -5192,10 +5192,10 @@
         <v>6</v>
       </c>
       <c r="V48" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W48" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49">
@@ -5227,12 +5227,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_03.jpg</t>
+          <t>stimuli/guitar/guitar_17.jpg</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_05.jpg</t>
+          <t>stimuli/bread/bread_22.jpg</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5247,22 +5247,22 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -5271,14 +5271,14 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S49" t="n">
@@ -5291,10 +5291,10 @@
         <v>9</v>
       </c>
       <c r="V49" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W49" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_33.jpg</t>
+          <t>stimuli/jacket/jacket_05.jpg</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/ball/ball_14.jpg</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5346,38 +5346,38 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0.8</v>
+        <v>0.47</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S50" t="n">
@@ -5390,10 +5390,10 @@
         <v>8</v>
       </c>
       <c r="V50" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="W50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_17.jpg</t>
+          <t>stimuli/pencil/pencil_21.jpg</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_31.jpg</t>
+          <t>stimuli/bread/bread_22.jpg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5445,17 +5445,17 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5465,18 +5465,18 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.6</v>
+        <v>0.33</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S51" t="n">
@@ -5489,10 +5489,10 @@
         <v>4</v>
       </c>
       <c r="V51" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W51" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -5524,14 +5524,14 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
+          <t>stimuli/guitar/guitar_17.jpg</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_31.jpg</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_22.jpg</t>
-        </is>
-      </c>
       <c r="I52" t="inlineStr">
         <is>
           <t>chair</t>
@@ -5544,22 +5544,22 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
+          <t>guitar</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
           <t>dog</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5568,14 +5568,14 @@
         </is>
       </c>
       <c r="P52" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q52" t="n">
         <v>0.67</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0.4</v>
-      </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S52" t="n">
@@ -5588,10 +5588,10 @@
         <v>15</v>
       </c>
       <c r="V52" t="n">
+        <v>13</v>
+      </c>
+      <c r="W52" t="n">
         <v>5</v>
-      </c>
-      <c r="W52" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_03.jpg</t>
+          <t>stimuli/bread/bread_22.jpg</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_50.jpg</t>
+          <t>stimuli/guitar/guitar_17.jpg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5658,19 +5658,19 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0.8</v>
+        <v>0.47</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.4</v>
+        <v>0.26</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
@@ -5687,10 +5687,10 @@
         <v>16</v>
       </c>
       <c r="V53" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="W53" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54">
@@ -5722,12 +5722,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/ball/ball_50.jpg</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_08.jpg</t>
+          <t>stimuli/phone/phone_27.jpg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5742,22 +5742,22 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5766,14 +5766,14 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S54" t="n">
@@ -5786,10 +5786,10 @@
         <v>12</v>
       </c>
       <c r="V54" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W54" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="55">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_25.jpg</t>
+          <t>stimuli/house/house_49.jpg</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_27.jpg</t>
+          <t>stimuli/chair/chair_26.jpg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5841,38 +5841,38 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.25</v>
+        <v>0.42</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S55" t="n">
@@ -5885,10 +5885,10 @@
         <v>3</v>
       </c>
       <c r="V55" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W55" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_39.jpg</t>
+          <t>stimuli/flower/flower_25.jpg</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_08.jpg</t>
+          <t>stimuli/phone/phone_27.jpg</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5940,22 +5940,22 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -5964,14 +5964,14 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.42</v>
+        <v>0.31</v>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S56" t="n">
@@ -5984,10 +5984,10 @@
         <v>9</v>
       </c>
       <c r="V56" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W56" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="57">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_27.jpg</t>
+          <t>stimuli/guitar/guitar_38.jpg</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6059,18 +6059,18 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P57" t="n">
         <v>0.53</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S57" t="n">
@@ -6086,7 +6086,7 @@
         <v>4</v>
       </c>
       <c r="W57" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="58">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_38.jpg</t>
+          <t>stimuli/bicycle/bicycle_08.jpg</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6143,33 +6143,33 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P58" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S58" t="n">
@@ -6185,7 +6185,7 @@
         <v>10</v>
       </c>
       <c r="W58" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/fish/fish_26.jpg</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_08.jpg</t>
+          <t>stimuli/house/house_49.jpg</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6237,17 +6237,17 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6257,18 +6257,18 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0.8</v>
+        <v>0.33</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.58</v>
+        <v>0.2</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S59" t="n">
@@ -6281,10 +6281,10 @@
         <v>1</v>
       </c>
       <c r="V59" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="W59" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_35.jpg</t>
+          <t>stimuli/hammer/hammer_39.jpg</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/phone/phone_27.jpg</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6351,19 +6351,19 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0.47</v>
+        <v>0.75</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.2</v>
+        <v>0.53</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
@@ -6380,10 +6380,10 @@
         <v>8</v>
       </c>
       <c r="V60" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="W60" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="61">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/phone/phone_27.jpg</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_25.jpg</t>
+          <t>stimuli/bread/bread_15.jpg</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6450,19 +6450,19 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0.33</v>
+        <v>0.58</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="R61" t="inlineStr">
         <is>
@@ -6479,10 +6479,10 @@
         <v>10</v>
       </c>
       <c r="V61" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="W61" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_35.jpg</t>
+          <t>stimuli/dog/dog_40.jpg</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6544,28 +6544,28 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0.6</v>
+        <v>0.33</v>
       </c>
       <c r="Q62" t="n">
         <v>0.2</v>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S62" t="n">
@@ -6578,7 +6578,7 @@
         <v>7</v>
       </c>
       <c r="V62" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="W62" t="n">
         <v>1</v>
@@ -6613,12 +6613,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_26.jpg</t>
+          <t>stimuli/bicycle/bicycle_08.jpg</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/hand/hand_24.jpg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6633,12 +6633,12 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -6657,10 +6657,10 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
@@ -6677,10 +6677,10 @@
         <v>4</v>
       </c>
       <c r="V63" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="W63" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64">
@@ -6712,12 +6712,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_15.jpg</t>
+          <t>stimuli/lamp/lamp_35.jpg</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/flower/flower_25.jpg</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6747,19 +6747,19 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.27</v>
+        <v>0.4</v>
       </c>
       <c r="R64" t="inlineStr">
         <is>
@@ -6776,10 +6776,10 @@
         <v>2</v>
       </c>
       <c r="V64" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="W64" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_35.jpg</t>
+          <t>stimuli/bread/bread_15.jpg</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/jacket/jacket_15.jpg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6831,38 +6831,38 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.53</v>
+        <v>0.27</v>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S65" t="n">
@@ -6875,10 +6875,10 @@
         <v>13</v>
       </c>
       <c r="V65" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="W65" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="66">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_26.jpg</t>
+          <t>stimuli/house/house_49.jpg</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/lamp/lamp_35.jpg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6930,38 +6930,38 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.67</v>
+        <v>0.26</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S66" t="n">
@@ -6974,10 +6974,10 @@
         <v>17</v>
       </c>
       <c r="V66" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="W66" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="67">
@@ -7009,12 +7009,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_05.jpg</t>
+          <t>stimuli/hammer/hammer_50.jpg</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>stimuli/key/key_13.jpg</t>
+          <t>stimuli/pencil/pencil_21.jpg</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -7029,38 +7029,38 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0.75</v>
+        <v>0.53</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S67" t="n">
@@ -7073,10 +7073,10 @@
         <v>14</v>
       </c>
       <c r="V67" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W67" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="68">
@@ -7108,12 +7108,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/flower/flower_01.jpg</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_33.jpg</t>
+          <t>stimuli/key/key_13.jpg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7128,38 +7128,38 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0.64</v>
+        <v>0.53</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S68" t="n">
@@ -7172,10 +7172,10 @@
         <v>5</v>
       </c>
       <c r="V68" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W68" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_01.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>stimuli/key/key_13.jpg</t>
+          <t>stimuli/pencil/pencil_21.jpg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -7227,38 +7227,38 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0.58</v>
+        <v>0.8</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S69" t="n">
@@ -7271,10 +7271,10 @@
         <v>10</v>
       </c>
       <c r="V69" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="W69" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="70">
@@ -7306,12 +7306,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/house/house_23.jpg</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_21.jpg</t>
+          <t>stimuli/key/key_13.jpg</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -7326,17 +7326,17 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -7346,18 +7346,18 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0.75</v>
+        <v>0.58</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S70" t="n">
@@ -7370,10 +7370,10 @@
         <v>2</v>
       </c>
       <c r="V70" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="W70" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="71">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_50.jpg</t>
+          <t>stimuli/flower/flower_01.jpg</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7440,16 +7440,16 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q71" t="n">
         <v>0.58</v>
@@ -7469,7 +7469,7 @@
         <v>1</v>
       </c>
       <c r="V71" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W71" t="n">
         <v>8</v>
@@ -7504,12 +7504,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/chair/chair_33.jpg</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_33.jpg</t>
+          <t>stimuli/pencil/pencil_21.jpg</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7524,38 +7524,38 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S72" t="n">
@@ -7568,10 +7568,10 @@
         <v>3</v>
       </c>
       <c r="V72" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="W72" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="73">
@@ -7603,14 +7603,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
+          <t>stimuli/house/house_23.jpg</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_31.jpg</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_11.jpg</t>
-        </is>
-      </c>
       <c r="I73" t="inlineStr">
         <is>
           <t>bread</t>
@@ -7623,22 +7623,22 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
           <t>dog</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -7647,14 +7647,14 @@
         </is>
       </c>
       <c r="P73" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Q73" t="n">
         <v>0.33</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0.2</v>
-      </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S73" t="n">
@@ -7667,10 +7667,10 @@
         <v>7</v>
       </c>
       <c r="V73" t="n">
+        <v>9</v>
+      </c>
+      <c r="W73" t="n">
         <v>5</v>
-      </c>
-      <c r="W73" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -7707,7 +7707,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_03.jpg</t>
+          <t>stimuli/ball/ball_14.jpg</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7727,12 +7727,12 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -7742,18 +7742,18 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P74" t="n">
         <v>0.58</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.47</v>
+        <v>0.2</v>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S74" t="n">
@@ -7769,7 +7769,7 @@
         <v>16</v>
       </c>
       <c r="W74" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_17.jpg</t>
+          <t>stimuli/lamp/lamp_03.jpg</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_11.jpg</t>
+          <t>stimuli/jacket/jacket_05.jpg</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7821,22 +7821,22 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7845,14 +7845,14 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0.6</v>
+        <v>0.53</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S75" t="n">
@@ -7865,10 +7865,10 @@
         <v>9</v>
       </c>
       <c r="V75" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W75" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_05.jpg</t>
+          <t>stimuli/guitar/guitar_17.jpg</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -7935,19 +7935,19 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0.47</v>
+        <v>0.67</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
@@ -7964,10 +7964,10 @@
         <v>8</v>
       </c>
       <c r="V76" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="W76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -7999,12 +7999,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>stimuli/key/key_13.jpg</t>
+          <t>stimuli/jacket/jacket_05.jpg</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_50.jpg</t>
+          <t>stimuli/bread/bread_22.jpg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -8019,12 +8019,12 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8034,19 +8034,19 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0.8</v>
+        <v>0.53</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
@@ -8063,10 +8063,10 @@
         <v>4</v>
       </c>
       <c r="V77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="W77" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_31.jpg</t>
+          <t>stimuli/pencil/pencil_21.jpg</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -8142,7 +8142,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="Q78" t="n">
         <v>0.27</v>
@@ -8162,7 +8162,7 @@
         <v>15</v>
       </c>
       <c r="V78" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="W78" t="n">
         <v>6</v>
@@ -8197,12 +8197,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_03.jpg</t>
+          <t>stimuli/dog/dog_31.jpg</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/guitar/guitar_17.jpg</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -8217,17 +8217,17 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -8237,18 +8237,18 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S79" t="n">
@@ -8261,10 +8261,10 @@
         <v>16</v>
       </c>
       <c r="V79" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="W79" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="80">
@@ -8296,12 +8296,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_15.jpg</t>
+          <t>stimuli/jacket/jacket_15.jpg</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_39.jpg</t>
+          <t>stimuli/phone/phone_27.jpg</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -8340,10 +8340,10 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0.8</v>
+        <v>0.47</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.42</v>
+        <v>0.2</v>
       </c>
       <c r="R80" t="inlineStr">
         <is>
@@ -8360,10 +8360,10 @@
         <v>12</v>
       </c>
       <c r="V80" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W80" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="81">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_39.jpg</t>
+          <t>stimuli/ball/ball_50.jpg</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8425,28 +8425,28 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0.47</v>
+        <v>0.64</v>
       </c>
       <c r="Q81" t="n">
         <v>0.36</v>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S81" t="n">
@@ -8459,7 +8459,7 @@
         <v>3</v>
       </c>
       <c r="V81" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="W81" t="n">
         <v>2</v>
@@ -8494,12 +8494,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_26.jpg</t>
+          <t>stimuli/hammer/hammer_39.jpg</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_27.jpg</t>
+          <t>stimuli/guitar/guitar_38.jpg</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8514,17 +8514,17 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -8534,18 +8534,18 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S82" t="n">
@@ -8558,10 +8558,10 @@
         <v>9</v>
       </c>
       <c r="V82" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W82" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83">
@@ -8593,12 +8593,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/flower/flower_25.jpg</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_38.jpg</t>
+          <t>stimuli/phone/phone_27.jpg</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8613,22 +8613,22 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -8637,14 +8637,14 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S83" t="n">
@@ -8657,10 +8657,10 @@
         <v>5</v>
       </c>
       <c r="V83" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W83" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="84">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_15.jpg</t>
+          <t>stimuli/chair/chair_26.jpg</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_38.jpg</t>
+          <t>stimuli/phone/phone_27.jpg</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8811,38 +8811,38 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S85" t="n">
@@ -8855,10 +8855,10 @@
         <v>1</v>
       </c>
       <c r="V85" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="W85" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="86">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_35.jpg</t>
+          <t>stimuli/bread/bread_15.jpg</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -8920,28 +8920,28 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="Q86" t="n">
         <v>0.2</v>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S86" t="n">
@@ -8954,7 +8954,7 @@
         <v>8</v>
       </c>
       <c r="V86" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="W86" t="n">
         <v>5</v>
@@ -8989,12 +8989,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_15.jpg</t>
+          <t>stimuli/chair/chair_26.jpg</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_25.jpg</t>
+          <t>stimuli/fish/fish_26.jpg</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -9009,38 +9009,38 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.2</v>
+        <v>0.47</v>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S87" t="n">
@@ -9053,10 +9053,10 @@
         <v>10</v>
       </c>
       <c r="V87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W87" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="88">
@@ -9118,12 +9118,12 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S88" t="n">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_38.jpg</t>
+          <t>stimuli/phone/phone_27.jpg</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_26.jpg</t>
+          <t>stimuli/hand/hand_24.jpg</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -9207,12 +9207,12 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -9231,10 +9231,10 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="R89" t="inlineStr">
         <is>
@@ -9251,10 +9251,10 @@
         <v>4</v>
       </c>
       <c r="V89" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="W89" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_26.jpg</t>
+          <t>stimuli/bread/bread_15.jpg</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/ball/ball_50.jpg</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -9306,38 +9306,38 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S90" t="n">
@@ -9350,10 +9350,10 @@
         <v>2</v>
       </c>
       <c r="V90" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="W90" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -9385,12 +9385,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_35.jpg</t>
+          <t>stimuli/house/house_49.jpg</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/jacket/jacket_15.jpg</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -9429,10 +9429,10 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.6</v>
+        <v>0.27</v>
       </c>
       <c r="R91" t="inlineStr">
         <is>
@@ -9449,10 +9449,10 @@
         <v>13</v>
       </c>
       <c r="V91" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="W91" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="92">
@@ -9514,17 +9514,17 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P92" t="n">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S92" t="n">
@@ -9583,12 +9583,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_31.jpg</t>
+          <t>stimuli/jacket/jacket_05.jpg</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_28.jpg</t>
+          <t>stimuli/pencil/pencil_21.jpg</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -9603,38 +9603,38 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.36</v>
+        <v>0.2</v>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S93" t="n">
@@ -9647,10 +9647,10 @@
         <v>14</v>
       </c>
       <c r="V93" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W93" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="94">
@@ -9712,17 +9712,17 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P94" t="n">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S94" t="n">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/hand/hand_28.jpg</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -9825,14 +9825,14 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="Q95" t="n">
         <v>0.31</v>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S95" t="n">
@@ -9845,7 +9845,7 @@
         <v>10</v>
       </c>
       <c r="V95" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W95" t="n">
         <v>16</v>
@@ -9880,12 +9880,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/flower/flower_01.jpg</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_28.jpg</t>
+          <t>stimuli/key/key_13.jpg</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -9900,22 +9900,22 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -9924,14 +9924,14 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0.8</v>
+        <v>0.64</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.53</v>
+        <v>0.42</v>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S96" t="n">
@@ -9944,10 +9944,10 @@
         <v>2</v>
       </c>
       <c r="V96" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W96" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="97">
@@ -9979,7 +9979,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/bread/bread_22.jpg</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -9999,7 +9999,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -10014,16 +10014,16 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="Q97" t="n">
         <v>0.53</v>
@@ -10043,7 +10043,7 @@
         <v>1</v>
       </c>
       <c r="V97" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="W97" t="n">
         <v>4</v>
@@ -10108,12 +10108,12 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S98" t="n">
@@ -10177,12 +10177,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_31.jpg</t>
+          <t>stimuli/house/house_23.jpg</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_11.jpg</t>
+          <t>stimuli/chair/chair_33.jpg</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -10197,38 +10197,38 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.2</v>
+        <v>0.64</v>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S99" t="n">
@@ -10241,10 +10241,10 @@
         <v>7</v>
       </c>
       <c r="V99" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W99" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="100">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>stimuli/key/key_13.jpg</t>
+          <t>stimuli/lamp/lamp_03.jpg</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_03.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -10296,12 +10296,12 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -10320,10 +10320,10 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0.64</v>
+        <v>0.47</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.47</v>
+        <v>0.27</v>
       </c>
       <c r="R100" t="inlineStr">
         <is>
@@ -10340,10 +10340,10 @@
         <v>6</v>
       </c>
       <c r="V100" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W100" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_05.jpg</t>
+          <t>stimuli/dog/dog_31.jpg</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/ball/ball_14.jpg</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -10410,19 +10410,19 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R101" t="inlineStr">
         <is>
@@ -10439,10 +10439,10 @@
         <v>9</v>
       </c>
       <c r="V101" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W101" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -10504,17 +10504,17 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P102" t="n">
@@ -10525,7 +10525,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S102" t="n">
@@ -10573,12 +10573,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_03.jpg</t>
+          <t>stimuli/guitar/guitar_17.jpg</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_01.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -10593,38 +10593,38 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.2</v>
+        <v>0.47</v>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S103" t="n">
@@ -10637,10 +10637,10 @@
         <v>4</v>
       </c>
       <c r="V103" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W103" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -10672,12 +10672,12 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_31.jpg</t>
+          <t>stimuli/jacket/jacket_05.jpg</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_11.jpg</t>
+          <t>stimuli/bread/bread_22.jpg</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -10692,38 +10692,38 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="Q104" t="n">
-        <v>0.53</v>
+        <v>0.4</v>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S104" t="n">
@@ -10736,10 +10736,10 @@
         <v>15</v>
       </c>
       <c r="V104" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">

--- a/psychopy_exp_files/sequences/learning_block2_fixed-middle-10_09.xlsx
+++ b/psychopy_exp_files/sequences/learning_block2_fixed-middle-10_09.xlsx
@@ -668,7 +668,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_15.jpg</t>
+          <t>stimuli/ball/ball_50.jpg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -734,7 +734,7 @@
         <v>12</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V3" t="n">
         <v>7</v>
@@ -762,42 +762,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_50.jpg</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_24.jpg</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_49.jpg</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_15.jpg</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_49.jpg</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_50.jpg</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_08.jpg</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>bread</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>bicycle</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -830,16 +830,16 @@
         <v>4</v>
       </c>
       <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>8</v>
+      </c>
+      <c r="V4" t="n">
+        <v>9</v>
+      </c>
+      <c r="W4" t="n">
         <v>3</v>
-      </c>
-      <c r="U4" t="n">
-        <v>9</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -861,7 +861,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/hand/hand_24.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -929,7 +929,7 @@
         <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U5" t="n">
         <v>5</v>
@@ -965,14 +965,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_08.jpg</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_25.jpg</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_24.jpg</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>stimuli/phone/phone_27.jpg</t>
@@ -985,12 +985,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>hand</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1031,10 +1031,10 @@
         <v>5</v>
       </c>
       <c r="U6" t="n">
+        <v>2</v>
+      </c>
+      <c r="V6" t="n">
         <v>6</v>
-      </c>
-      <c r="V6" t="n">
-        <v>8</v>
       </c>
       <c r="W6" t="n">
         <v>17</v>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_25.jpg</t>
+          <t>stimuli/bicycle/bicycle_08.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_50.jpg</t>
+          <t>stimuli/house/house_49.jpg</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1127,10 +1127,10 @@
         <v>7</v>
       </c>
       <c r="T7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="V7" t="n">
         <v>4</v>
@@ -1158,42 +1158,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_50.jpg</t>
+          <t>stimuli/house/house_49.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_25.jpg</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>stimuli/guitar/guitar_38.jpg</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_24.jpg</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>stimuli/guitar/guitar_38.jpg</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_49.jpg</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>guitar</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>hand</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>guitar</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>house</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>8</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="U8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V8" t="n">
         <v>13</v>
       </c>
       <c r="W8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/flower/flower_25.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1325,7 +1325,7 @@
         <v>9</v>
       </c>
       <c r="T9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U9" t="n">
         <v>10</v>
@@ -1366,12 +1366,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/hand/hand_24.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_25.jpg</t>
+          <t>stimuli/bicycle/bicycle_08.jpg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1430,10 +1430,10 @@
         <v>7</v>
       </c>
       <c r="V10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_15.jpg</t>
+          <t>stimuli/ball/ball_50.jpg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1532,7 +1532,7 @@
         <v>14</v>
       </c>
       <c r="W11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_08.jpg</t>
+          <t>stimuli/bread/bread_15.jpg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1625,7 +1625,7 @@
         <v>4</v>
       </c>
       <c r="U12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V12" t="n">
         <v>12</v>
@@ -1653,42 +1653,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_15.jpg</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>stimuli/guitar/guitar_38.jpg</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_35.jpg</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_08.jpg</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>stimuli/guitar/guitar_38.jpg</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>stimuli/lamp/lamp_35.jpg</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_25.jpg</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>guitar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t>bicycle</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>guitar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>lamp</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1721,7 +1721,7 @@
         <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
         <v>13</v>
@@ -1730,7 +1730,7 @@
         <v>14</v>
       </c>
       <c r="W13" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_11.jpg</t>
+          <t>stimuli/bread/bread_22.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2024,7 +2024,7 @@
         <v>5</v>
       </c>
       <c r="V16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W16" t="n">
         <v>16</v>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/ball/ball_14.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2123,7 +2123,7 @@
         <v>10</v>
       </c>
       <c r="V17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W17" t="n">
         <v>15</v>
@@ -2153,17 +2153,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_11.jpg</t>
+          <t>stimuli/bread/bread_22.jpg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_23.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_28.jpg</t>
+          <t>stimuli/flower/flower_01.jpg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2173,17 +2173,17 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2219,13 +2219,13 @@
         <v>10</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V18" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="W18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_11.jpg</t>
+          <t>stimuli/bread/bread_22.jpg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_23.jpg</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2315,10 +2315,10 @@
         <v>6</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="V19" t="n">
         <v>13</v>
@@ -2346,14 +2346,14 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>stimuli/house/house_23.jpg</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>stimuli/ball/ball_14.jpg</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_22.jpg</t>
-        </is>
-      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>stimuli/hammer/hammer_50.jpg</t>
@@ -2366,12 +2366,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>ball</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bread</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2414,10 +2414,10 @@
         <v>7</v>
       </c>
       <c r="T20" t="n">
+        <v>9</v>
+      </c>
+      <c r="U20" t="n">
         <v>1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>3</v>
       </c>
       <c r="V20" t="n">
         <v>7</v>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/ball/ball_14.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/hand/hand_28.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2513,13 +2513,13 @@
         <v>8</v>
       </c>
       <c r="T21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
         <v>7</v>
       </c>
       <c r="V21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W21" t="n">
         <v>4</v>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_01.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_23.jpg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2615,13 +2615,13 @@
         <v>7</v>
       </c>
       <c r="U22" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="V22" t="n">
         <v>14</v>
       </c>
       <c r="W22" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_01.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/hand/hand_28.jpg</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2658,17 +2658,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/ball/ball_14.jpg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2711,16 +2711,16 @@
         <v>10</v>
       </c>
       <c r="T23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V23" t="n">
         <v>10</v>
       </c>
       <c r="W23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -2742,12 +2742,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/hand/hand_28.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_28.jpg</t>
+          <t>stimuli/flower/flower_01.jpg</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2762,12 +2762,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2810,10 +2810,10 @@
         <v>11</v>
       </c>
       <c r="T24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V24" t="n">
         <v>14</v>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_28.jpg</t>
+          <t>stimuli/flower/flower_01.jpg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2856,12 +2856,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_01.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2909,7 +2909,7 @@
         <v>12</v>
       </c>
       <c r="T25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U25" t="n">
         <v>4</v>
@@ -2918,7 +2918,7 @@
         <v>13</v>
       </c>
       <c r="W25" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/flower/flower_25.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_08.jpg</t>
+          <t>stimuli/bread/bread_15.jpg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3212,10 +3212,10 @@
         <v>12</v>
       </c>
       <c r="V28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_15.jpg</t>
+          <t>stimuli/ball/ball_50.jpg</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3308,7 +3308,7 @@
         <v>12</v>
       </c>
       <c r="U29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V29" t="n">
         <v>7</v>
@@ -3336,19 +3336,19 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_50.jpg</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_24.jpg</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_15.jpg</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_49.jpg</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_08.jpg</t>
-        </is>
-      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>stimuli/phone/phone_27.jpg</t>
@@ -3356,17 +3356,17 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t>bread</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>bicycle</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3404,13 +3404,13 @@
         <v>4</v>
       </c>
       <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>8</v>
+      </c>
+      <c r="V30" t="n">
         <v>3</v>
-      </c>
-      <c r="U30" t="n">
-        <v>9</v>
-      </c>
-      <c r="V30" t="n">
-        <v>2</v>
       </c>
       <c r="W30" t="n">
         <v>17</v>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/hand/hand_24.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_25.jpg</t>
+          <t>stimuli/bicycle/bicycle_08.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3503,13 +3503,13 @@
         <v>5</v>
       </c>
       <c r="T31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U31" t="n">
         <v>5</v>
       </c>
       <c r="V31" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="W31" t="n">
         <v>14</v>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_25.jpg</t>
+          <t>stimuli/bicycle/bicycle_08.jpg</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3605,7 +3605,7 @@
         <v>5</v>
       </c>
       <c r="U32" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="V32" t="n">
         <v>10</v>
@@ -3633,19 +3633,19 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_08.jpg</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_49.jpg</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_25.jpg</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_50.jpg</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_24.jpg</t>
-        </is>
-      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>stimuli/chair/chair_26.jpg</t>
@@ -3653,17 +3653,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>hand</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3701,13 +3701,13 @@
         <v>7</v>
       </c>
       <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>9</v>
+      </c>
+      <c r="V33" t="n">
         <v>6</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1</v>
-      </c>
-      <c r="V33" t="n">
-        <v>8</v>
       </c>
       <c r="W33" t="n">
         <v>4</v>
@@ -3732,42 +3732,42 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_50.jpg</t>
+          <t>stimuli/house/house_49.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_25.jpg</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>stimuli/fish/fish_26.jpg</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_24.jpg</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>stimuli/fish/fish_26.jpg</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_49.jpg</t>
-        </is>
-      </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fish</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t>hand</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fish</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>house</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3800,16 +3800,16 @@
         <v>8</v>
       </c>
       <c r="T34" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="U34" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V34" t="n">
         <v>12</v>
       </c>
       <c r="W34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/flower/flower_25.jpg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3899,7 +3899,7 @@
         <v>9</v>
       </c>
       <c r="T35" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U35" t="n">
         <v>10</v>
@@ -3940,14 +3940,14 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_24.jpg</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
           <t>stimuli/house/house_49.jpg</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_50.jpg</t>
-        </is>
-      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>jacket</t>
@@ -3960,12 +3960,12 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
           <t>house</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>ball</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4004,10 +4004,10 @@
         <v>7</v>
       </c>
       <c r="V36" t="n">
+        <v>8</v>
+      </c>
+      <c r="W36" t="n">
         <v>9</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -4039,12 +4039,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_15.jpg</t>
+          <t>stimuli/ball/ball_50.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_25.jpg</t>
+          <t>stimuli/bicycle/bicycle_08.jpg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4059,12 +4059,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4103,10 +4103,10 @@
         <v>4</v>
       </c>
       <c r="V37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W37" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_08.jpg</t>
+          <t>stimuli/bread/bread_15.jpg</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/hand/hand_24.jpg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4199,13 +4199,13 @@
         <v>4</v>
       </c>
       <c r="U38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V38" t="n">
         <v>14</v>
       </c>
       <c r="W38" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_08.jpg</t>
+          <t>stimuli/bread/bread_15.jpg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/flower/flower_25.jpg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4295,7 +4295,7 @@
         <v>13</v>
       </c>
       <c r="T39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U39" t="n">
         <v>13</v>
@@ -4304,7 +4304,7 @@
         <v>12</v>
       </c>
       <c r="W39" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_15.jpg</t>
+          <t>stimuli/ball/ball_50.jpg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4400,7 +4400,7 @@
         <v>17</v>
       </c>
       <c r="V40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W40" t="n">
         <v>5</v>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_11.jpg</t>
+          <t>stimuli/bread/bread_22.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4499,7 +4499,7 @@
         <v>14</v>
       </c>
       <c r="V41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W41" t="n">
         <v>16</v>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_23.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4697,7 +4697,7 @@
         <v>10</v>
       </c>
       <c r="V43" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="W43" t="n">
         <v>15</v>
@@ -4727,17 +4727,17 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_11.jpg</t>
+          <t>stimuli/bread/bread_22.jpg</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/ball/ball_14.jpg</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_28.jpg</t>
+          <t>stimuli/flower/flower_01.jpg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4747,17 +4747,17 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4793,13 +4793,13 @@
         <v>10</v>
       </c>
       <c r="U44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W44" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
@@ -4821,19 +4821,19 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_22.jpg</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_23.jpg</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_14.jpg</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_01.jpg</t>
-        </is>
-      </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>stimuli/pencil/pencil_21.jpg</t>
@@ -4841,17 +4841,17 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t>bicycle</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4889,13 +4889,13 @@
         <v>6</v>
       </c>
       <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>9</v>
+      </c>
+      <c r="V45" t="n">
         <v>2</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1</v>
-      </c>
-      <c r="V45" t="n">
-        <v>6</v>
       </c>
       <c r="W45" t="n">
         <v>16</v>
@@ -4920,14 +4920,14 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
+          <t>stimuli/house/house_23.jpg</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>stimuli/ball/ball_14.jpg</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_22.jpg</t>
-        </is>
-      </c>
       <c r="G46" t="inlineStr">
         <is>
           <t>stimuli/hammer/hammer_50.jpg</t>
@@ -4935,19 +4935,19 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/hand/hand_28.jpg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
           <t>ball</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
       <c r="K46" t="inlineStr">
         <is>
           <t>hammer</t>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4988,16 +4988,16 @@
         <v>7</v>
       </c>
       <c r="T46" t="n">
+        <v>9</v>
+      </c>
+      <c r="U46" t="n">
         <v>1</v>
-      </c>
-      <c r="U46" t="n">
-        <v>3</v>
       </c>
       <c r="V46" t="n">
         <v>7</v>
       </c>
       <c r="W46" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47">
@@ -5019,42 +5019,42 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_14.jpg</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>stimuli/hammer/hammer_50.jpg</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_31.jpg</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_22.jpg</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_50.jpg</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_31.jpg</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_11.jpg</t>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
           <t>bread</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>bicycle</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5087,7 +5087,7 @@
         <v>8</v>
       </c>
       <c r="T47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U47" t="n">
         <v>7</v>
@@ -5096,7 +5096,7 @@
         <v>5</v>
       </c>
       <c r="W47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_01.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -5189,7 +5189,7 @@
         <v>7</v>
       </c>
       <c r="U48" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="V48" t="n">
         <v>16</v>
@@ -5217,12 +5217,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_01.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/hand/hand_28.jpg</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5232,17 +5232,17 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/ball/ball_14.jpg</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5285,16 +5285,16 @@
         <v>10</v>
       </c>
       <c r="T49" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V49" t="n">
         <v>13</v>
       </c>
       <c r="W49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -5316,42 +5316,42 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_28.jpg</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>stimuli/flower/flower_01.jpg</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>stimuli/jacket/jacket_05.jpg</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
           <t>stimuli/house/house_23.jpg</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_28.jpg</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_05.jpg</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_14.jpg</t>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
           <t>house</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>ball</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5384,16 +5384,16 @@
         <v>11</v>
       </c>
       <c r="T50" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U50" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V50" t="n">
         <v>10</v>
       </c>
       <c r="W50" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_28.jpg</t>
+          <t>stimuli/flower/flower_01.jpg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/ball/ball_14.jpg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5483,7 +5483,7 @@
         <v>12</v>
       </c>
       <c r="T51" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U51" t="n">
         <v>4</v>
@@ -5492,7 +5492,7 @@
         <v>16</v>
       </c>
       <c r="W51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/ball/ball_14.jpg</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5687,7 +5687,7 @@
         <v>16</v>
       </c>
       <c r="V53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W53" t="n">
         <v>13</v>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_50.jpg</t>
+          <t>stimuli/house/house_49.jpg</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5786,7 +5786,7 @@
         <v>12</v>
       </c>
       <c r="V54" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="W54" t="n">
         <v>17</v>
@@ -5816,12 +5816,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_15.jpg</t>
+          <t>stimuli/ball/ball_50.jpg</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/hand/hand_24.jpg</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5836,12 +5836,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5882,10 +5882,10 @@
         <v>12</v>
       </c>
       <c r="U55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V55" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W55" t="n">
         <v>4</v>
@@ -5910,17 +5910,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_15.jpg</t>
+          <t>stimuli/ball/ball_50.jpg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/hand/hand_24.jpg</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_25.jpg</t>
+          <t>stimuli/bicycle/bicycle_08.jpg</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5930,17 +5930,17 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5978,13 +5978,13 @@
         <v>4</v>
       </c>
       <c r="T56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U56" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V56" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="W56" t="n">
         <v>17</v>
@@ -6009,7 +6009,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/hand/hand_24.jpg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6077,7 +6077,7 @@
         <v>5</v>
       </c>
       <c r="T57" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U57" t="n">
         <v>5</v>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_25.jpg</t>
+          <t>stimuli/bicycle/bicycle_08.jpg</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_08.jpg</t>
+          <t>stimuli/bread/bread_15.jpg</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6179,13 +6179,13 @@
         <v>5</v>
       </c>
       <c r="U58" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="V58" t="n">
         <v>10</v>
       </c>
       <c r="W58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_25.jpg</t>
+          <t>stimuli/bicycle/bicycle_08.jpg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_50.jpg</t>
+          <t>stimuli/house/house_49.jpg</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -6222,17 +6222,17 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/hand/hand_24.jpg</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6275,16 +6275,16 @@
         <v>7</v>
       </c>
       <c r="T59" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U59" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="V59" t="n">
         <v>12</v>
       </c>
       <c r="W59" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60">
@@ -6306,12 +6306,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_50.jpg</t>
+          <t>stimuli/house/house_49.jpg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/flower/flower_25.jpg</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -6326,12 +6326,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -6374,10 +6374,10 @@
         <v>8</v>
       </c>
       <c r="T60" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="U60" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V60" t="n">
         <v>7</v>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/flower/flower_25.jpg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -6420,12 +6420,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_15.jpg</t>
+          <t>stimuli/ball/ball_50.jpg</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6473,7 +6473,7 @@
         <v>9</v>
       </c>
       <c r="T61" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U61" t="n">
         <v>10</v>
@@ -6482,7 +6482,7 @@
         <v>17</v>
       </c>
       <c r="W61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_50.jpg</t>
+          <t>stimuli/house/house_49.jpg</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -6581,7 +6581,7 @@
         <v>5</v>
       </c>
       <c r="W62" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63">
@@ -6613,12 +6613,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_08.jpg</t>
+          <t>stimuli/bread/bread_15.jpg</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/flower/flower_25.jpg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6633,12 +6633,12 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -6677,10 +6677,10 @@
         <v>4</v>
       </c>
       <c r="V63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W63" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64">
@@ -6707,19 +6707,19 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_15.jpg</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_35.jpg</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_08.jpg</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>stimuli/lamp/lamp_35.jpg</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_25.jpg</t>
-        </is>
-      </c>
       <c r="I64" t="inlineStr">
         <is>
           <t>chair</t>
@@ -6727,17 +6727,17 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
           <t>bicycle</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>lamp</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6773,13 +6773,13 @@
         <v>4</v>
       </c>
       <c r="U64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V64" t="n">
         <v>14</v>
       </c>
       <c r="W64" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_08.jpg</t>
+          <t>stimuli/bread/bread_15.jpg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_15.jpg</t>
+          <t>stimuli/ball/ball_50.jpg</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6869,13 +6869,13 @@
         <v>13</v>
       </c>
       <c r="T65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U65" t="n">
         <v>13</v>
       </c>
       <c r="V65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W65" t="n">
         <v>10</v>
@@ -6910,7 +6910,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/hand/hand_24.jpg</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6974,7 +6974,7 @@
         <v>17</v>
       </c>
       <c r="V66" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W66" t="n">
         <v>14</v>
@@ -7108,7 +7108,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_01.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -7172,7 +7172,7 @@
         <v>5</v>
       </c>
       <c r="V68" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="W68" t="n">
         <v>15</v>
@@ -7207,7 +7207,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_11.jpg</t>
+          <t>stimuli/bread/bread_22.jpg</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7227,7 +7227,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -7271,7 +7271,7 @@
         <v>10</v>
       </c>
       <c r="V69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W69" t="n">
         <v>16</v>
@@ -7301,12 +7301,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_11.jpg</t>
+          <t>stimuli/bread/bread_22.jpg</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/hand/hand_28.jpg</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7321,12 +7321,12 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -7367,10 +7367,10 @@
         <v>10</v>
       </c>
       <c r="U70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V70" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W70" t="n">
         <v>15</v>
@@ -7395,42 +7395,42 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_22.jpg</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_23.jpg</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_14.jpg</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>stimuli/flower/flower_01.jpg</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_28.jpg</t>
-        </is>
-      </c>
       <c r="I71" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t>bicycle</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>hand</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -7463,16 +7463,16 @@
         <v>6</v>
       </c>
       <c r="T71" t="n">
+        <v>3</v>
+      </c>
+      <c r="U71" t="n">
+        <v>9</v>
+      </c>
+      <c r="V71" t="n">
         <v>2</v>
       </c>
-      <c r="U71" t="n">
-        <v>1</v>
-      </c>
-      <c r="V71" t="n">
+      <c r="W71" t="n">
         <v>6</v>
-      </c>
-      <c r="W71" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="72">
@@ -7494,14 +7494,14 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
+          <t>stimuli/house/house_23.jpg</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t>stimuli/ball/ball_14.jpg</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_22.jpg</t>
-        </is>
-      </c>
       <c r="G72" t="inlineStr">
         <is>
           <t>stimuli/chair/chair_33.jpg</t>
@@ -7514,12 +7514,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
           <t>ball</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>bread</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7562,10 +7562,10 @@
         <v>7</v>
       </c>
       <c r="T72" t="n">
+        <v>9</v>
+      </c>
+      <c r="U72" t="n">
         <v>1</v>
-      </c>
-      <c r="U72" t="n">
-        <v>3</v>
       </c>
       <c r="V72" t="n">
         <v>4</v>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/ball/ball_14.jpg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/hand/hand_28.jpg</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7661,13 +7661,13 @@
         <v>8</v>
       </c>
       <c r="T73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U73" t="n">
         <v>7</v>
       </c>
       <c r="V73" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W73" t="n">
         <v>5</v>
@@ -7697,7 +7697,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_01.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -7707,7 +7707,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_14.jpg</t>
+          <t>stimuli/house/house_23.jpg</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -7763,13 +7763,13 @@
         <v>7</v>
       </c>
       <c r="U74" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="V74" t="n">
         <v>16</v>
       </c>
       <c r="W74" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="75">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_01.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/hand/hand_28.jpg</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -7811,12 +7811,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7859,10 +7859,10 @@
         <v>10</v>
       </c>
       <c r="T75" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U75" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V75" t="n">
         <v>14</v>
@@ -7890,12 +7890,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/hand/hand_28.jpg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_28.jpg</t>
+          <t>stimuli/flower/flower_01.jpg</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -7905,17 +7905,17 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_11.jpg</t>
+          <t>stimuli/bread/bread_22.jpg</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -7958,16 +7958,16 @@
         <v>11</v>
       </c>
       <c r="T76" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U76" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V76" t="n">
         <v>13</v>
       </c>
       <c r="W76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
@@ -7989,7 +7989,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_28.jpg</t>
+          <t>stimuli/flower/flower_01.jpg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -8004,12 +8004,12 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/ball/ball_14.jpg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8057,7 +8057,7 @@
         <v>12</v>
       </c>
       <c r="T77" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U77" t="n">
         <v>4</v>
@@ -8066,7 +8066,7 @@
         <v>10</v>
       </c>
       <c r="W77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_01.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -8123,7 +8123,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8165,7 +8165,7 @@
         <v>16</v>
       </c>
       <c r="W78" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -8390,19 +8390,19 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_50.jpg</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_49.jpg</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_15.jpg</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_50.jpg</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_08.jpg</t>
-        </is>
-      </c>
       <c r="I81" t="inlineStr">
         <is>
           <t>fish</t>
@@ -8410,17 +8410,17 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
           <t>bread</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>bicycle</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -8456,13 +8456,13 @@
         <v>12</v>
       </c>
       <c r="U81" t="n">
+        <v>1</v>
+      </c>
+      <c r="V81" t="n">
+        <v>9</v>
+      </c>
+      <c r="W81" t="n">
         <v>3</v>
-      </c>
-      <c r="V81" t="n">
-        <v>1</v>
-      </c>
-      <c r="W81" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_15.jpg</t>
+          <t>stimuli/ball/ball_50.jpg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/hand/hand_24.jpg</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -8552,10 +8552,10 @@
         <v>4</v>
       </c>
       <c r="T82" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U82" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V82" t="n">
         <v>7</v>
@@ -8583,7 +8583,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/hand/hand_24.jpg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -8593,7 +8593,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_25.jpg</t>
+          <t>stimuli/bicycle/bicycle_08.jpg</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -8603,7 +8603,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -8651,13 +8651,13 @@
         <v>5</v>
       </c>
       <c r="T83" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U83" t="n">
         <v>5</v>
       </c>
       <c r="V83" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="W83" t="n">
         <v>17</v>
@@ -8687,7 +8687,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_25.jpg</t>
+          <t>stimuli/bicycle/bicycle_08.jpg</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -8697,7 +8697,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_15.jpg</t>
+          <t>stimuli/ball/ball_50.jpg</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -8753,13 +8753,13 @@
         <v>5</v>
       </c>
       <c r="U84" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="V84" t="n">
         <v>14</v>
       </c>
       <c r="W84" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_25.jpg</t>
+          <t>stimuli/bicycle/bicycle_08.jpg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_50.jpg</t>
+          <t>stimuli/house/house_49.jpg</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -8849,10 +8849,10 @@
         <v>7</v>
       </c>
       <c r="T85" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U85" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="V85" t="n">
         <v>4</v>
@@ -8880,19 +8880,19 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
+          <t>stimuli/house/house_49.jpg</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>stimuli/flower/flower_25.jpg</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
           <t>stimuli/ball/ball_50.jpg</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_24.jpg</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_15.jpg</t>
-        </is>
-      </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>stimuli/dog/dog_40.jpg</t>
@@ -8900,17 +8900,17 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t>ball</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>bread</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -8948,13 +8948,13 @@
         <v>8</v>
       </c>
       <c r="T86" t="n">
+        <v>9</v>
+      </c>
+      <c r="U86" t="n">
+        <v>6</v>
+      </c>
+      <c r="V86" t="n">
         <v>1</v>
-      </c>
-      <c r="U86" t="n">
-        <v>8</v>
-      </c>
-      <c r="V86" t="n">
-        <v>3</v>
       </c>
       <c r="W86" t="n">
         <v>5</v>
@@ -8979,7 +8979,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/flower/flower_25.jpg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -9047,7 +9047,7 @@
         <v>9</v>
       </c>
       <c r="T87" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U87" t="n">
         <v>10</v>
@@ -9088,14 +9088,14 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_24.jpg</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
           <t>stimuli/house/house_49.jpg</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_50.jpg</t>
-        </is>
-      </c>
       <c r="I88" t="inlineStr">
         <is>
           <t>jacket</t>
@@ -9108,12 +9108,12 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
           <t>house</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>ball</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -9152,10 +9152,10 @@
         <v>7</v>
       </c>
       <c r="V88" t="n">
+        <v>8</v>
+      </c>
+      <c r="W88" t="n">
         <v>9</v>
-      </c>
-      <c r="W88" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_24.jpg</t>
+          <t>stimuli/flower/flower_25.jpg</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -9254,7 +9254,7 @@
         <v>17</v>
       </c>
       <c r="W89" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90">
@@ -9281,17 +9281,17 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_08.jpg</t>
+          <t>stimuli/bread/bread_15.jpg</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_15.jpg</t>
+          <t>stimuli/ball/ball_50.jpg</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_50.jpg</t>
+          <t>stimuli/house/house_49.jpg</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -9301,17 +9301,17 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -9347,13 +9347,13 @@
         <v>4</v>
       </c>
       <c r="U90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V90" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W90" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="91">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_08.jpg</t>
+          <t>stimuli/bread/bread_15.jpg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -9385,7 +9385,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>stimuli/house/house_49.jpg</t>
+          <t>stimuli/hand/hand_24.jpg</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -9443,13 +9443,13 @@
         <v>13</v>
       </c>
       <c r="T91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U91" t="n">
         <v>13</v>
       </c>
       <c r="V91" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W91" t="n">
         <v>10</v>
@@ -9484,7 +9484,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_15.jpg</t>
+          <t>stimuli/ball/ball_50.jpg</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -9504,7 +9504,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -9548,7 +9548,7 @@
         <v>17</v>
       </c>
       <c r="V92" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W92" t="n">
         <v>7</v>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_28.jpg</t>
+          <t>stimuli/flower/flower_01.jpg</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -9845,7 +9845,7 @@
         <v>10</v>
       </c>
       <c r="V95" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W95" t="n">
         <v>16</v>
@@ -9875,14 +9875,14 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_22.jpg</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_01.jpg</t>
-        </is>
-      </c>
       <c r="H96" t="inlineStr">
         <is>
           <t>stimuli/key/key_13.jpg</t>
@@ -9895,12 +9895,12 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t>bicycle</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -9941,10 +9941,10 @@
         <v>10</v>
       </c>
       <c r="U96" t="n">
+        <v>3</v>
+      </c>
+      <c r="V96" t="n">
         <v>2</v>
-      </c>
-      <c r="V96" t="n">
-        <v>6</v>
       </c>
       <c r="W96" t="n">
         <v>15</v>
@@ -9969,19 +9969,19 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_11.jpg</t>
+          <t>stimuli/bread/bread_22.jpg</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
+          <t>stimuli/house/house_23.jpg</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
           <t>stimuli/ball/ball_14.jpg</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_22.jpg</t>
-        </is>
-      </c>
       <c r="H97" t="inlineStr">
         <is>
           <t>stimuli/chair/chair_33.jpg</t>
@@ -9989,17 +9989,17 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t>ball</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>bread</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -10037,13 +10037,13 @@
         <v>6</v>
       </c>
       <c r="T97" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U97" t="n">
+        <v>9</v>
+      </c>
+      <c r="V97" t="n">
         <v>1</v>
-      </c>
-      <c r="V97" t="n">
-        <v>3</v>
       </c>
       <c r="W97" t="n">
         <v>4</v>
@@ -10068,14 +10068,14 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
+          <t>stimuli/house/house_23.jpg</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
           <t>stimuli/ball/ball_14.jpg</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_22.jpg</t>
-        </is>
-      </c>
       <c r="G98" t="inlineStr">
         <is>
           <t>stimuli/guitar/guitar_17.jpg</t>
@@ -10088,12 +10088,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
           <t>ball</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>bread</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -10136,10 +10136,10 @@
         <v>7</v>
       </c>
       <c r="T98" t="n">
+        <v>9</v>
+      </c>
+      <c r="U98" t="n">
         <v>1</v>
-      </c>
-      <c r="U98" t="n">
-        <v>3</v>
       </c>
       <c r="V98" t="n">
         <v>13</v>
@@ -10167,7 +10167,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/ball/ball_14.jpg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/hand/hand_28.jpg</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -10235,13 +10235,13 @@
         <v>8</v>
       </c>
       <c r="T99" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U99" t="n">
         <v>7</v>
       </c>
       <c r="V99" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W99" t="n">
         <v>4</v>
@@ -10271,7 +10271,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_01.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_11.jpg</t>
+          <t>stimuli/bread/bread_22.jpg</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -10337,13 +10337,13 @@
         <v>7</v>
       </c>
       <c r="U100" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="V100" t="n">
         <v>14</v>
       </c>
       <c r="W100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
@@ -10365,42 +10365,42 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_01.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_28.jpg</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_31.jpg</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
           <t>stimuli/house/house_23.jpg</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_31.jpg</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_14.jpg</t>
-        </is>
-      </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
           <t>house</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>ball</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -10433,16 +10433,16 @@
         <v>10</v>
       </c>
       <c r="T101" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U101" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V101" t="n">
         <v>5</v>
       </c>
       <c r="W101" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="102">
@@ -10464,12 +10464,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>stimuli/house/house_23.jpg</t>
+          <t>stimuli/hand/hand_28.jpg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_28.jpg</t>
+          <t>stimuli/flower/flower_01.jpg</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -10532,10 +10532,10 @@
         <v>11</v>
       </c>
       <c r="T102" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U102" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V102" t="n">
         <v>4</v>
@@ -10563,7 +10563,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_28.jpg</t>
+          <t>stimuli/flower/flower_01.jpg</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -10578,12 +10578,12 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_11.jpg</t>
+          <t>stimuli/bread/bread_22.jpg</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -10598,7 +10598,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -10631,7 +10631,7 @@
         <v>12</v>
       </c>
       <c r="T103" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U103" t="n">
         <v>4</v>
@@ -10640,7 +10640,7 @@
         <v>13</v>
       </c>
       <c r="W103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -10677,7 +10677,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_22.jpg</t>
+          <t>stimuli/ball/ball_14.jpg</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -10739,7 +10739,7 @@
         <v>10</v>
       </c>
       <c r="W104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -10776,7 +10776,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_01.jpg</t>
+          <t>stimuli/bicycle/bicycle_11.jpg</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -10796,7 +10796,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -10838,7 +10838,7 @@
         <v>14</v>
       </c>
       <c r="W105" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
